--- a/docs/PPG/Bolsas.xlsx
+++ b/docs/PPG/Bolsas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2502A5C-5086-084E-B99C-8A8AF06C5E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B5F4C4-305F-4B4A-BC2C-0B9BFB1033B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="680" windowWidth="27900" windowHeight="17500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="680" windowWidth="27900" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UNISUAM" sheetId="9" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="173">
   <si>
     <t>Portaria nº 123 de 01 de agosto de 2013</t>
   </si>
@@ -548,15 +548,31 @@
   </si>
   <si>
     <t>https://cad.capes.gov.br/ato-administrativo-detalhar?idAtoAdmElastic=20431</t>
+  </si>
+  <si>
+    <t>https://www.in.gov.br/web/dou/-/portaria-capes-n-397-de-17-de-setembro-de-2026-732627675</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>PORTARIA CAPES Nº 397, DE 17 DE SETEMBRO DE 2026 - Altera a Portaria CAPES n.º 209, de 8 de maio de 2026, que dispõe sobre a prorrogação do período de vigência das bolsas de pós-graduação stricto sensu concedidas pela CAPES no País, em razão de parto, nascimento de filho, adoção ou obtenção de guarda judicial para fins de adoção.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -794,181 +810,190 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -976,9 +1001,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1622,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE69CE70-DFA3-5E49-A523-CFA0DDA93B5C}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" style="37" customWidth="1"/>
@@ -1642,213 +1664,213 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="75" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" s="73" t="s">
+    <row r="2" spans="1:3" s="75" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="75" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="73" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B3" s="74" t="s">
         <v>168</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C3" s="15" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="71" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="72" t="s">
+    <row r="4" spans="1:3" s="71" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B4" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C4" s="15" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="51" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="55" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="51" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="51" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
         <v>139</v>
       </c>
       <c r="B5" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="51" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C6" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="49" customFormat="1" ht="68" x14ac:dyDescent="0.2">
-      <c r="A6" s="48" t="s">
+    <row r="7" spans="1:3" s="49" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="A7" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B7" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C7" s="15" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="47" t="s">
+    <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B8" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C8" s="23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="38" t="s">
         <v>118</v>
       </c>
       <c r="B9" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C10" s="23" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="39" t="s">
+    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B11" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C11" s="23" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+    <row r="12" spans="1:3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B12" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="60" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="60" t="s">
+      <c r="B14" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C14" s="15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="43" t="s">
+    <row r="15" spans="1:3" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="65" t="s">
+      <c r="B15" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+    <row r="16" spans="1:3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B16" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="41" t="s">
+    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="61" t="s">
+      <c r="B17" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C17" s="15" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="60" t="s">
+      <c r="B19" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C19" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+    <row r="20" spans="1:3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="64" t="s">
+      <c r="B20" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="62" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -1856,94 +1878,106 @@
         <v>18</v>
       </c>
       <c r="B21" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C22" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+    <row r="23" spans="1:3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="64" t="s">
+      <c r="B23" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="41" t="s">
+    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="B23" s="61" t="s">
+      <c r="B24" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C24" s="15" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="43" t="s">
+    <row r="25" spans="1:3" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="65" t="s">
+      <c r="B25" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C27" s="15" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C20" r:id="rId1" xr:uid="{CFDB1A8B-BF62-D246-9D7A-DB8C40CEF4B0}"/>
-    <hyperlink ref="C21" r:id="rId2" xr:uid="{B927918F-7565-E542-B802-C6455BEC1726}"/>
-    <hyperlink ref="C25" r:id="rId3" location="anchor" xr:uid="{C4BED215-1CC6-5946-90A3-16810EF37D52}"/>
-    <hyperlink ref="C26" r:id="rId4" xr:uid="{2392AA86-0182-A541-A1BE-117DBA331788}"/>
-    <hyperlink ref="C13" r:id="rId5" xr:uid="{D0F7BA5B-9F0E-C041-A414-C338681AC4D9}"/>
-    <hyperlink ref="C17" r:id="rId6" xr:uid="{5D6B074E-AF30-E249-83E0-5E3312A3270E}"/>
-    <hyperlink ref="C12" r:id="rId7" xr:uid="{C8363C0D-FEB4-FC4C-85EC-82E5E8CF621A}"/>
-    <hyperlink ref="C18" r:id="rId8" display="https://sei.capes.gov.br/sei/controlador_externo.php?acao=documento_conferir&amp;codigo_verificador=1122002&amp;codigo_crc=289939CB&amp;hash_download=449b3b0fc962c24d73fdabf1d13929e9016def4302529547c91b7327cb18bab31821b9633c211abb41d021eafd5081cf129ba2af16cb5d49fbade44f102740d4&amp;visualizacao=1&amp;id_orgao_acesso_externo=0" xr:uid="{93A5AC1D-1ECD-D542-B23E-B63CEFC59AA1}"/>
-    <hyperlink ref="C23" r:id="rId9" display="https://sei.capes.gov.br/sei/controlador_externo.php?acao=documento_conferir&amp;codigo_verificador=0339325&amp;codigo_crc=499CC556&amp;hash_download=877c0950a7536647184dd1e3a1c9414d0995405e078be7824fe7258b89e6db6fe8b07ef4f2ec02b91da337bd1d653374c718f6617aa4414ac6548e63aeee0c66&amp;visualizacao=1&amp;id_orgao_acesso_externo=0" xr:uid="{6FC038AD-2D31-FD43-AB00-749DDE76B733}"/>
-    <hyperlink ref="C16" r:id="rId10" display="https://sei.capes.gov.br/sei/controlador_externo.php?acao=documento_conferir&amp;codigo_verificador=1604656&amp;codigo_crc=3876C0B0&amp;hash_download=17f26cc19c93d5cc93be2d0f7491d9c7523c30e3d7bae0d0961cbb5add014aa3d640ee0f2797947fe37116df2d11ed1264bade2249d647e09080fae8594b7e97&amp;visualizacao=1&amp;id_orgao_acesso_externo=0" xr:uid="{BE20119B-2DC3-604F-858B-F8B3B465C6A5}"/>
-    <hyperlink ref="C10" r:id="rId11" xr:uid="{8A1ADAC6-9AA9-F74E-81A5-558BD0B6AE8E}"/>
-    <hyperlink ref="C8" r:id="rId12" xr:uid="{7DEE1662-6085-6048-A1C7-DF7B04B5FADD}"/>
-    <hyperlink ref="C9" r:id="rId13" xr:uid="{7F5C11A0-076A-634E-8B00-FC1902655798}"/>
-    <hyperlink ref="C11" r:id="rId14" xr:uid="{6944FE21-1C9C-B94D-81F5-1BE2E1F176FE}"/>
-    <hyperlink ref="C19" r:id="rId15" xr:uid="{D55FC383-6BB1-2A40-A0A7-C3C5ABD4E3D4}"/>
-    <hyperlink ref="C15" r:id="rId16" xr:uid="{EDE1F38C-D6D5-904B-81E7-5C17BD574614}"/>
-    <hyperlink ref="C22" r:id="rId17" xr:uid="{2924B1AE-6C7A-AF49-8876-BA5D606E8B92}"/>
-    <hyperlink ref="C24" r:id="rId18" xr:uid="{6A018B38-6AC6-7541-A415-8E16D447DB38}"/>
-    <hyperlink ref="C14" r:id="rId19" xr:uid="{18EE8016-E6DE-D648-ACA7-63DD117F2DA2}"/>
-    <hyperlink ref="C7" r:id="rId20" xr:uid="{56994366-5984-1C40-BBD4-436A7D3ECDA2}"/>
-    <hyperlink ref="C6" r:id="rId21" location="anchor" xr:uid="{71838580-F419-0849-815A-7C00172C9307}"/>
-    <hyperlink ref="C5" r:id="rId22" xr:uid="{A5501423-474A-654A-8AB7-E3C85724D7CD}"/>
-    <hyperlink ref="C4" r:id="rId23" xr:uid="{2B3EFA27-27D0-354C-84F7-8E92F116C152}"/>
-    <hyperlink ref="C3" r:id="rId24" xr:uid="{6E38D56E-44BC-1E42-99C9-C3B7C935130F}"/>
-    <hyperlink ref="C2" r:id="rId25" xr:uid="{FAB8A511-97C4-BA46-ADE8-6906DA1F55C9}"/>
+    <hyperlink ref="C21" r:id="rId1" xr:uid="{CFDB1A8B-BF62-D246-9D7A-DB8C40CEF4B0}"/>
+    <hyperlink ref="C22" r:id="rId2" xr:uid="{B927918F-7565-E542-B802-C6455BEC1726}"/>
+    <hyperlink ref="C26" r:id="rId3" location="anchor" xr:uid="{C4BED215-1CC6-5946-90A3-16810EF37D52}"/>
+    <hyperlink ref="C27" r:id="rId4" xr:uid="{2392AA86-0182-A541-A1BE-117DBA331788}"/>
+    <hyperlink ref="C14" r:id="rId5" xr:uid="{D0F7BA5B-9F0E-C041-A414-C338681AC4D9}"/>
+    <hyperlink ref="C18" r:id="rId6" xr:uid="{5D6B074E-AF30-E249-83E0-5E3312A3270E}"/>
+    <hyperlink ref="C13" r:id="rId7" xr:uid="{C8363C0D-FEB4-FC4C-85EC-82E5E8CF621A}"/>
+    <hyperlink ref="C19" r:id="rId8" display="https://sei.capes.gov.br/sei/controlador_externo.php?acao=documento_conferir&amp;codigo_verificador=1122002&amp;codigo_crc=289939CB&amp;hash_download=449b3b0fc962c24d73fdabf1d13929e9016def4302529547c91b7327cb18bab31821b9633c211abb41d021eafd5081cf129ba2af16cb5d49fbade44f102740d4&amp;visualizacao=1&amp;id_orgao_acesso_externo=0" xr:uid="{93A5AC1D-1ECD-D542-B23E-B63CEFC59AA1}"/>
+    <hyperlink ref="C24" r:id="rId9" display="https://sei.capes.gov.br/sei/controlador_externo.php?acao=documento_conferir&amp;codigo_verificador=0339325&amp;codigo_crc=499CC556&amp;hash_download=877c0950a7536647184dd1e3a1c9414d0995405e078be7824fe7258b89e6db6fe8b07ef4f2ec02b91da337bd1d653374c718f6617aa4414ac6548e63aeee0c66&amp;visualizacao=1&amp;id_orgao_acesso_externo=0" xr:uid="{6FC038AD-2D31-FD43-AB00-749DDE76B733}"/>
+    <hyperlink ref="C17" r:id="rId10" display="https://sei.capes.gov.br/sei/controlador_externo.php?acao=documento_conferir&amp;codigo_verificador=1604656&amp;codigo_crc=3876C0B0&amp;hash_download=17f26cc19c93d5cc93be2d0f7491d9c7523c30e3d7bae0d0961cbb5add014aa3d640ee0f2797947fe37116df2d11ed1264bade2249d647e09080fae8594b7e97&amp;visualizacao=1&amp;id_orgao_acesso_externo=0" xr:uid="{BE20119B-2DC3-604F-858B-F8B3B465C6A5}"/>
+    <hyperlink ref="C11" r:id="rId11" xr:uid="{8A1ADAC6-9AA9-F74E-81A5-558BD0B6AE8E}"/>
+    <hyperlink ref="C9" r:id="rId12" xr:uid="{7DEE1662-6085-6048-A1C7-DF7B04B5FADD}"/>
+    <hyperlink ref="C10" r:id="rId13" xr:uid="{7F5C11A0-076A-634E-8B00-FC1902655798}"/>
+    <hyperlink ref="C12" r:id="rId14" xr:uid="{6944FE21-1C9C-B94D-81F5-1BE2E1F176FE}"/>
+    <hyperlink ref="C20" r:id="rId15" xr:uid="{D55FC383-6BB1-2A40-A0A7-C3C5ABD4E3D4}"/>
+    <hyperlink ref="C16" r:id="rId16" xr:uid="{EDE1F38C-D6D5-904B-81E7-5C17BD574614}"/>
+    <hyperlink ref="C23" r:id="rId17" xr:uid="{2924B1AE-6C7A-AF49-8876-BA5D606E8B92}"/>
+    <hyperlink ref="C25" r:id="rId18" xr:uid="{6A018B38-6AC6-7541-A415-8E16D447DB38}"/>
+    <hyperlink ref="C15" r:id="rId19" xr:uid="{18EE8016-E6DE-D648-ACA7-63DD117F2DA2}"/>
+    <hyperlink ref="C8" r:id="rId20" xr:uid="{56994366-5984-1C40-BBD4-436A7D3ECDA2}"/>
+    <hyperlink ref="C7" r:id="rId21" location="anchor" xr:uid="{71838580-F419-0849-815A-7C00172C9307}"/>
+    <hyperlink ref="C6" r:id="rId22" xr:uid="{A5501423-474A-654A-8AB7-E3C85724D7CD}"/>
+    <hyperlink ref="C5" r:id="rId23" xr:uid="{2B3EFA27-27D0-354C-84F7-8E92F116C152}"/>
+    <hyperlink ref="C4" r:id="rId24" xr:uid="{6E38D56E-44BC-1E42-99C9-C3B7C935130F}"/>
+    <hyperlink ref="C3" r:id="rId25" xr:uid="{FAB8A511-97C4-BA46-ADE8-6906DA1F55C9}"/>
+    <hyperlink ref="C2" r:id="rId26" xr:uid="{D0662B58-C63A-5C46-8E62-D085D0C80869}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
